--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260727.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260727.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>97,069,000</t>
+          <t>3,423,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>3,423,000</t>
+          <t>97,069,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
